--- a/feedback_forms/033_meeting_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/033_meeting_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>attendee_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Meeting Attendee's Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>attendee_email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,15 +589,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>feedback_comments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Share your experience during the meeting</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +611,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>meeting_feedback_form_page_2</t>
+          <t>meeting_helpfulness_rating</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Meeting Feedback Form</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Rate the Meeting's Helpfulness</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select your rating</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,12 +643,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>meeting_feedback_form_page_3</t>
+          <t>attended_other_meetings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Meeting Feedback Form</t>
+          <t>Attended Other Meetings</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,24 +661,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>most_valuable_takeaway</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>This meeting was very helpful.</t>
-        </is>
-      </c>
+          <t>Most Valuable Takeaway</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -685,16 +689,124 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>meeting_feedback_form_page_4</t>
+          <t>meeting_relevance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Meeting Feedback Form</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Meeting Relevance</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Was the meeting relevant to your goals?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>meeting_duration</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Meeting Duration</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>meeting_on_time</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Meeting On Time</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Was the meeting scheduled on time?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>technical_issues</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Technical Issues</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Were there any technical difficulties during the meeting?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>suggestions</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Suggestions</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>What can we improve for future meetings?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -714,9 +826,9 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -739,51 +851,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>meeting_helpfulness_rating_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Very good</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>meeting_helpfulness_rating_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>meeting_helpfulness_rating_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>very_bad</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Very bad</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
